--- a/healthcare_surveys/050_healthcare_accessibility_plan_evaluation_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/050_healthcare_accessibility_plan_evaluation_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>automatic_door</t>
+          <t>wide_doorways</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Automatic door</t>
+          <t>Wide doorways</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>wide_doorways</t>
+          <t>wide_doorways_and_hallways</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wide doorways</t>
+          <t>Wide doorways and hallways</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>wide_doorways_and_hallways</t>
+          <t>accessible_parking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wide doorways and hallways</t>
+          <t>Accessible parking</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>accessible_parking</t>
+          <t>accessible_restrooms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Accessible parking</t>
+          <t>Accessible restrooms</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>accessible_parking</t>
+          <t>accessible_seating</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Accessible parking</t>
+          <t>Accessible seating</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>accessible_restrooms</t>
+          <t>accessible_waiting_area</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accessible restrooms</t>
+          <t>Accessible waiting area</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>accessible_seating</t>
+          <t>accessible_examination_room</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accessible seating</t>
+          <t>Accessible examination room</t>
         </is>
       </c>
     </row>
@@ -910,80 +910,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accessible_waiting_area</t>
+          <t>accessible_treatment_area</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accessible waiting area</t>
+          <t>Accessible treatment area</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>accessibility_features_choices</t>
+          <t>patient_feedback_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>accessible_examination_room</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Accessible examination room</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>accessibility_features_choices</t>
+          <t>patient_feedback_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>accessible_examination_room</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Accessible examination room</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>accessibility_features_choices</t>
+          <t>patient_feedback_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>accessible_treatment_area</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Accessible treatment area</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>accessibility_features_choices</t>
+          <t>patient_feedback_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>accessible_treatment_area</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accessible treatment area</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -995,80 +995,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>patient_feedback_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Somewhat satisfied</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>patient_feedback_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>patient_feedback_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Somewhat dissatisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>patient_feedback_choices</t>
+          <t>patient_satisfaction_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1080,78 +1080,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>patient_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>somewhat_satisfied</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Somewhat satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>patient_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>patient_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>somewhat_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Somewhat dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>patient_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Very dissatisfied</t>
         </is>
